--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ53"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6130,10 +6130,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2927187</v>
+        <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>98194</v>
+        <v>99259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,37 +6141,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220686</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Z336 Kall, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>394586</v>
+        <v>394561</v>
       </c>
       <c r="R49" t="n">
-        <v>7062184</v>
+        <v>7062335</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6195,12 +6195,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6211,45 +6211,35 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Steget Före</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2927187</t>
+          <t>https://artportalen.se/Sighting/136535740</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4387161</v>
+        <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99140</v>
+        <v>99259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,37 +6247,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sundet O, Jmt</t>
+          <t>Z336 Kall, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>394636</v>
+        <v>394527</v>
       </c>
       <c r="R50" t="n">
-        <v>7062291</v>
+        <v>7062310</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6311,12 +6301,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2010-06-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6327,83 +6317,73 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>grannaturskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Steget Före</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4387161</t>
+          <t>https://artportalen.se/Sighting/136535872</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122481467</v>
+        <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>78339</v>
+        <v>99259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Z336 Kall, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>394746</v>
+        <v>394791</v>
       </c>
       <c r="R51" t="n">
-        <v>7062338</v>
+        <v>7062390</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6427,12 +6407,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6443,84 +6423,73 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>bark på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122481467</t>
+          <t>https://artportalen.se/Sighting/136552103</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122481494</v>
+        <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>78339</v>
+        <v>99344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>219811</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Z336 Kall, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>394802</v>
+        <v>394525</v>
       </c>
       <c r="R52" t="n">
-        <v>7062015</v>
+        <v>7062309</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6544,12 +6513,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6560,84 +6529,73 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>barken på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122481494</t>
+          <t>https://artportalen.se/Sighting/136535956</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122483534</v>
+        <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>78338</v>
+        <v>99366</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6000248</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kådsvartspik</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis montana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Rikkinen</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sundet, Jmt</t>
+          <t>Z336 Kall, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>394734</v>
+        <v>394526</v>
       </c>
       <c r="R53" t="n">
-        <v>7062334</v>
+        <v>7062309</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6661,12 +6619,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6675,38 +6633,822 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136535061</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136535970</v>
+      </c>
+      <c r="B54" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Z336 Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>394558</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7062336</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136535970</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136536047</v>
+      </c>
+      <c r="B55" t="n">
+        <v>108367</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Z336 Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>394516</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7062303</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136536047</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2927187</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sundet O, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>394586</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7062184</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2927187</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4387161</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sundet O, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>394636</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7062291</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2010-06-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4387161</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122481467</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>394746</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7062338</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>bark på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481467</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122481494</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>394802</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7062015</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>barken på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122481494</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122483534</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78338</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6000248</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kådsvartspik</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis montana</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Rikkinen</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sundet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>394734</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7062334</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
           <t>Jesper Wadstein</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122483534</t>
         </is>
@@ -6766,6 +7508,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 45855-2024 artfynd.xlsx
+++ b/artfynd/A 45855-2024 artfynd.xlsx
@@ -6133,7 +6133,7 @@
         <v>136535740</v>
       </c>
       <c r="B49" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>136535872</v>
       </c>
       <c r="B50" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>136552103</v>
       </c>
       <c r="B51" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>136535956</v>
       </c>
       <c r="B52" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>136535061</v>
       </c>
       <c r="B53" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>136535970</v>
       </c>
       <c r="B54" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>136536047</v>
       </c>
       <c r="B55" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
